--- a/public/exports-with-coowners/29189676.xlsx
+++ b/public/exports-with-coowners/29189676.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238126</t>
+          <t xml:space="preserve">311238128</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">

--- a/public/exports-with-coowners/29189676.xlsx
+++ b/public/exports-with-coowners/29189676.xlsx
@@ -5629,12 +5629,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311238128</t>
+          <t xml:space="preserve">311238126</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
